--- a/Data Cleaning Excel Tutorial.xlsx
+++ b/Data Cleaning Excel Tutorial.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/Excel Series Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Data_Cleaning_In_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{C3F4832D-6691-4E80-9CE5-51C600B1F941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10770"/>
   </bookViews>
   <sheets>
     <sheet name="US_Presidents Excel Tutorial Da" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -448,10 +447,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -941,7 +940,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1296,14 +1295,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I48"/>
-  <sheetFormatPr defaultColWidth="23.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr defaultColWidth="23.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="23.5546875" style="3"/>
+    <col min="8" max="8" width="23.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1316,20 +1315,20 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>136</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1345,20 +1344,24 @@
       <c r="E2" t="s">
         <v>131</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="str">
+        <f>TRIM(G2:G48)</f>
+        <v>John Adams</v>
+      </c>
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4">
+      <c r="H2" s="4">
         <v>5000</v>
       </c>
-      <c r="H2" s="1">
-        <v>44391</v>
-      </c>
       <c r="I2" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J2" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1374,20 +1377,24 @@
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F48" si="0">TRIM(G3:G49)</f>
+        <v>Thomas Jefferson</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="4">
         <v>10000</v>
       </c>
-      <c r="H3" s="1">
-        <v>44391</v>
-      </c>
       <c r="I3" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J3" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1403,20 +1410,24 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>Aaron Burr</v>
+      </c>
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="4">
         <v>15000</v>
       </c>
-      <c r="H4" s="1">
-        <v>44391</v>
-      </c>
       <c r="I4" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J4" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1432,20 +1443,24 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>George Clinton</v>
+      </c>
+      <c r="G5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H5" s="4">
         <v>20000</v>
       </c>
-      <c r="H5" s="1">
-        <v>44391</v>
-      </c>
       <c r="I5" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J5" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1461,20 +1476,24 @@
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>Daniel D. Tompkins</v>
+      </c>
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="4">
         <v>25000</v>
       </c>
-      <c r="H6" s="1">
-        <v>44391</v>
-      </c>
       <c r="I6" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J6" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1490,20 +1509,24 @@
       <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>John C. Calhoun</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="4">
         <v>30000</v>
       </c>
-      <c r="H7" s="1">
-        <v>44391</v>
-      </c>
       <c r="I7" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J7" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1519,20 +1542,24 @@
       <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>John C. Calhoun</v>
+      </c>
+      <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="4">
         <v>35000</v>
       </c>
-      <c r="H8" s="1">
-        <v>44391</v>
-      </c>
       <c r="I8" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J8" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1548,20 +1575,24 @@
       <c r="E9" t="s">
         <v>26</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>Richard Mentor Johnson</v>
+      </c>
+      <c r="G9" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="4">
         <v>40000</v>
       </c>
-      <c r="H9" s="1">
-        <v>44391</v>
-      </c>
       <c r="I9" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J9" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1577,20 +1608,24 @@
       <c r="E10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>John Tyler</v>
+      </c>
+      <c r="G10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>45000</v>
       </c>
-      <c r="H10" s="1">
-        <v>44391</v>
-      </c>
       <c r="I10" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J10" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1606,20 +1641,24 @@
       <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>50000</v>
       </c>
-      <c r="H11" s="1">
-        <v>44391</v>
-      </c>
       <c r="I11" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J11" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1635,20 +1674,24 @@
       <c r="E12" t="s">
         <v>26</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>George M. Dallas</v>
+      </c>
+      <c r="G12" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>55000</v>
       </c>
-      <c r="H12" s="1">
-        <v>44391</v>
-      </c>
       <c r="I12" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J12" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1664,20 +1707,24 @@
       <c r="E13" t="s">
         <v>33</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>Millard Fillmore</v>
+      </c>
+      <c r="G13" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="4">
         <v>60000</v>
       </c>
-      <c r="H13" s="1">
-        <v>44391</v>
-      </c>
       <c r="I13" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J13" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1693,20 +1740,24 @@
       <c r="E14" t="s">
         <v>33</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G14" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>65000</v>
       </c>
-      <c r="H14" s="1">
-        <v>44391</v>
-      </c>
       <c r="I14" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J14" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1722,20 +1773,24 @@
       <c r="E15" t="s">
         <v>26</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>William R. King</v>
+      </c>
+      <c r="G15" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>75000</v>
       </c>
-      <c r="H15" s="1">
-        <v>44391</v>
-      </c>
       <c r="I15" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J15" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1751,20 +1806,24 @@
       <c r="E16" t="s">
         <v>26</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>John C. Breckinridge</v>
+      </c>
+      <c r="G16" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>85000</v>
       </c>
-      <c r="H16" s="1">
-        <v>44391</v>
-      </c>
       <c r="I16" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J16" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1780,20 +1839,24 @@
       <c r="E17" t="s">
         <v>60</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>Hannibal Hamlin</v>
+      </c>
+      <c r="G17" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="4">
+      <c r="H17" s="4">
         <v>95000</v>
       </c>
-      <c r="H17" s="1">
-        <v>44391</v>
-      </c>
       <c r="I17" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J17" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1809,20 +1872,24 @@
       <c r="E18" t="s">
         <v>26</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G18" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>105000</v>
       </c>
-      <c r="H18" s="1">
-        <v>44391</v>
-      </c>
       <c r="I18" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J18" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1838,20 +1905,24 @@
       <c r="E19" t="s">
         <v>60</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>Schuyler Colfax</v>
+      </c>
+      <c r="G19" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="4">
+      <c r="H19" s="4">
         <v>115000</v>
       </c>
-      <c r="H19" s="1">
-        <v>44391</v>
-      </c>
       <c r="I19" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J19" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1867,20 +1938,24 @@
       <c r="E20" t="s">
         <v>60</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>William A. Wheeler</v>
+      </c>
+      <c r="G20" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="4">
+      <c r="H20" s="4">
         <v>125000</v>
       </c>
-      <c r="H20" s="1">
-        <v>44391</v>
-      </c>
       <c r="I20" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J20" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1896,20 +1971,24 @@
       <c r="E21" t="s">
         <v>60</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>Chester A. Arthur</v>
+      </c>
+      <c r="G21" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="4">
+      <c r="H21" s="4">
         <v>135000</v>
       </c>
-      <c r="H21" s="1">
-        <v>44391</v>
-      </c>
       <c r="I21" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J21" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1925,20 +2004,24 @@
       <c r="E22" t="s">
         <v>60</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G22" t="s">
         <v>38</v>
       </c>
-      <c r="G22" s="4">
+      <c r="H22" s="4">
         <v>145000</v>
       </c>
-      <c r="H22" s="1">
-        <v>44391</v>
-      </c>
       <c r="I22" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J22" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1954,20 +2037,24 @@
       <c r="E23" t="s">
         <v>26</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>Thomas A. Hendricks</v>
+      </c>
+      <c r="G23" t="s">
         <v>71</v>
       </c>
-      <c r="G23" s="4">
+      <c r="H23" s="4">
         <v>155000</v>
       </c>
-      <c r="H23" s="1">
-        <v>44391</v>
-      </c>
       <c r="I23" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J23" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1983,20 +2070,24 @@
       <c r="E24" t="s">
         <v>60</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>Levi P. Morton</v>
+      </c>
+      <c r="G24" t="s">
         <v>74</v>
       </c>
-      <c r="G24" s="4">
+      <c r="H24" s="4">
         <v>165000</v>
       </c>
-      <c r="H24" s="1">
-        <v>44391</v>
-      </c>
       <c r="I24" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J24" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2012,20 +2103,24 @@
       <c r="E25" t="s">
         <v>26</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>Adlai Stevenson</v>
+      </c>
+      <c r="G25" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="4">
+      <c r="H25" s="4">
         <v>175000</v>
       </c>
-      <c r="H25" s="1">
-        <v>44391</v>
-      </c>
       <c r="I25" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J25" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2041,20 +2136,24 @@
       <c r="E26" t="s">
         <v>60</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>Garret Hobart</v>
+      </c>
+      <c r="G26" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="4">
+      <c r="H26" s="4">
         <v>185000</v>
       </c>
-      <c r="H26" s="1">
-        <v>44391</v>
-      </c>
       <c r="I26" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J26" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2070,20 +2169,24 @@
       <c r="E27" t="s">
         <v>60</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G27" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="4">
+      <c r="H27" s="4">
         <v>195000</v>
       </c>
-      <c r="H27" s="1">
-        <v>44391</v>
-      </c>
       <c r="I27" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J27" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2099,20 +2202,24 @@
       <c r="E28" t="s">
         <v>60</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>James S. Sherman</v>
+      </c>
+      <c r="G28" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="4">
+      <c r="H28" s="4">
         <v>205000</v>
       </c>
-      <c r="H28" s="1">
-        <v>44391</v>
-      </c>
       <c r="I28" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J28" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2128,20 +2235,24 @@
       <c r="E29" t="s">
         <v>26</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>Thomas R. Marshall</v>
+      </c>
+      <c r="G29" t="s">
         <v>87</v>
       </c>
-      <c r="G29" s="4">
+      <c r="H29" s="4">
         <v>225000</v>
       </c>
-      <c r="H29" s="1">
-        <v>44391</v>
-      </c>
       <c r="I29" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J29" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2157,20 +2268,24 @@
       <c r="E30" t="s">
         <v>133</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>Thomas R. Marshall</v>
+      </c>
+      <c r="G30" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="4">
+      <c r="H30" s="4">
         <v>225000</v>
       </c>
-      <c r="H30" s="1">
-        <v>44391</v>
-      </c>
       <c r="I30" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J30" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2186,20 +2301,24 @@
       <c r="E31" t="s">
         <v>60</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v>Calvin Coolidge</v>
+      </c>
+      <c r="G31" t="s">
         <v>90</v>
       </c>
-      <c r="G31" s="4">
+      <c r="H31" s="4">
         <v>235000</v>
       </c>
-      <c r="H31" s="1">
-        <v>44391</v>
-      </c>
       <c r="I31" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J31" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2215,20 +2334,24 @@
       <c r="E32" t="s">
         <v>60</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G32" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="4">
+      <c r="H32" s="4">
         <v>245000</v>
       </c>
-      <c r="H32" s="1">
-        <v>44391</v>
-      </c>
       <c r="I32" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J32" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2244,20 +2367,24 @@
       <c r="E33" t="s">
         <v>60</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v>Charles Curtis</v>
+      </c>
+      <c r="G33" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="4">
+      <c r="H33" s="4">
         <v>255000</v>
       </c>
-      <c r="H33" s="1">
-        <v>44391</v>
-      </c>
       <c r="I33" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J33" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2273,20 +2400,24 @@
       <c r="E34" t="s">
         <v>26</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v>John Nance Garner</v>
+      </c>
+      <c r="G34" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="4">
+      <c r="H34" s="4">
         <v>265000</v>
       </c>
-      <c r="H34" s="1">
-        <v>44391</v>
-      </c>
       <c r="I34" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J34" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2302,20 +2433,24 @@
       <c r="E35" t="s">
         <v>26</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G35" t="s">
         <v>38</v>
       </c>
-      <c r="G35" s="4">
+      <c r="H35" s="4">
         <v>275000</v>
       </c>
-      <c r="H35" s="1">
-        <v>44391</v>
-      </c>
       <c r="I35" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J35" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2331,20 +2466,24 @@
       <c r="E36" t="s">
         <v>60</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v>Richard Nixon</v>
+      </c>
+      <c r="G36" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="4">
+      <c r="H36" s="4">
         <v>285000</v>
       </c>
-      <c r="H36" s="1">
-        <v>44391</v>
-      </c>
       <c r="I36" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J36" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2360,20 +2499,24 @@
       <c r="E37" t="s">
         <v>26</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v>Lyndon B. Johnson</v>
+      </c>
+      <c r="G37" t="s">
         <v>105</v>
       </c>
-      <c r="G37" s="4">
+      <c r="H37" s="4">
         <v>295000</v>
       </c>
-      <c r="H37" s="1">
-        <v>44391</v>
-      </c>
       <c r="I37" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J37" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2389,20 +2532,24 @@
       <c r="E38" t="s">
         <v>26</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G38" t="s">
         <v>38</v>
       </c>
-      <c r="G38" s="4">
+      <c r="H38" s="4">
         <v>305000</v>
       </c>
-      <c r="H38" s="1">
-        <v>44391</v>
-      </c>
       <c r="I38" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J38" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2418,20 +2565,24 @@
       <c r="E39" t="s">
         <v>60</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v>Spiro Agnew</v>
+      </c>
+      <c r="G39" t="s">
         <v>108</v>
       </c>
-      <c r="G39" s="4">
+      <c r="H39" s="4">
         <v>315000</v>
       </c>
-      <c r="H39" s="1">
-        <v>44391</v>
-      </c>
       <c r="I39" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J39" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2447,20 +2598,24 @@
       <c r="E40" t="s">
         <v>60</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G40" t="s">
         <v>38</v>
       </c>
-      <c r="G40" s="4">
+      <c r="H40" s="4">
         <v>325000</v>
       </c>
-      <c r="H40" s="1">
-        <v>44391</v>
-      </c>
       <c r="I40" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J40" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
@@ -2476,20 +2631,24 @@
       <c r="E41" t="s">
         <v>26</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>Walter Mondale</v>
+      </c>
+      <c r="G41" t="s">
         <v>113</v>
       </c>
-      <c r="G41" s="4">
+      <c r="H41" s="4">
         <v>335000</v>
       </c>
-      <c r="H41" s="1">
-        <v>44391</v>
-      </c>
       <c r="I41" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J41" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
@@ -2505,20 +2664,24 @@
       <c r="E42" t="s">
         <v>60</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>George H. W. Bush</v>
+      </c>
+      <c r="G42" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="4">
+      <c r="H42" s="4">
         <v>345000</v>
       </c>
-      <c r="H42" s="1">
-        <v>44391</v>
-      </c>
       <c r="I42" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J42" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2534,20 +2697,24 @@
       <c r="E43" t="s">
         <v>60</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>Dan Quayle</v>
+      </c>
+      <c r="G43" t="s">
         <v>118</v>
       </c>
-      <c r="G43" s="4">
+      <c r="H43" s="4">
         <v>355000</v>
       </c>
-      <c r="H43" s="1">
-        <v>44391</v>
-      </c>
       <c r="I43" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J43" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
@@ -2563,20 +2730,24 @@
       <c r="E44" t="s">
         <v>26</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>Al Gore</v>
+      </c>
+      <c r="G44" t="s">
         <v>121</v>
       </c>
-      <c r="G44" s="4">
+      <c r="H44" s="4">
         <v>365000</v>
       </c>
-      <c r="H44" s="1">
-        <v>44391</v>
-      </c>
       <c r="I44" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J44" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
@@ -2592,20 +2763,24 @@
       <c r="E45" t="s">
         <v>60</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v>Dick Cheney</v>
+      </c>
+      <c r="G45" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="4">
+      <c r="H45" s="4">
         <v>375000</v>
       </c>
-      <c r="H45" s="1">
-        <v>44391</v>
-      </c>
       <c r="I45" s="1">
-        <v>40972</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44391</v>
+      </c>
+      <c r="J45" s="1">
+        <v>40972</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
@@ -2621,20 +2796,24 @@
       <c r="E46" t="s">
         <v>26</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>Joe Biden</v>
+      </c>
+      <c r="G46" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="4">
+      <c r="H46" s="4">
         <v>395000</v>
       </c>
-      <c r="H46" s="2">
-        <v>44391</v>
-      </c>
       <c r="I46" s="2">
+        <v>44391</v>
+      </c>
+      <c r="J46" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -2650,20 +2829,24 @@
       <c r="E47" t="s">
         <v>26</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v>Joe Biden</v>
+      </c>
+      <c r="G47" t="s">
         <v>127</v>
       </c>
-      <c r="G47" s="4">
+      <c r="H47" s="4">
         <v>395000</v>
       </c>
-      <c r="H47" s="2">
-        <v>44391</v>
-      </c>
       <c r="I47" s="2">
+        <v>44391</v>
+      </c>
+      <c r="J47" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>44</v>
       </c>
@@ -2679,16 +2862,20 @@
       <c r="E48" t="s">
         <v>132</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v>Mike Pence</v>
+      </c>
+      <c r="G48" t="s">
         <v>130</v>
       </c>
-      <c r="G48" s="4">
+      <c r="H48" s="4">
         <v>405000</v>
       </c>
-      <c r="H48" s="2">
-        <v>44391</v>
-      </c>
       <c r="I48" s="2">
+        <v>44391</v>
+      </c>
+      <c r="J48" s="2">
         <v>43862</v>
       </c>
     </row>

--- a/Data Cleaning Excel Tutorial.xlsx
+++ b/Data Cleaning Excel Tutorial.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="137">
   <si>
     <t>S.No.</t>
   </si>
@@ -448,8 +448,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  <numFmts count="1">
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
@@ -935,10 +934,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1299,7 +1297,7 @@
   <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="23.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="23.5703125" style="3"/>
+    <col min="7" max="7" width="23.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1318,13 +1316,13 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1348,7 +1346,7 @@
       <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>5000</v>
       </c>
       <c r="H2" s="1">
@@ -1372,13 +1370,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E48" si="0">TRIM(F3:F49)</f>
+        <f>TRIM(F3:F49)</f>
         <v>Thomas Jefferson</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>10000</v>
       </c>
       <c r="H3" s="1">
@@ -1402,13 +1400,13 @@
         <v>13</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F4:F50)</f>
         <v>Aaron Burr</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>15000</v>
       </c>
       <c r="H4" s="1">
@@ -1432,13 +1430,13 @@
         <v>13</v>
       </c>
       <c r="E5" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F5:F51)</f>
         <v>George Clinton</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>20000</v>
       </c>
       <c r="H5" s="1">
@@ -1462,13 +1460,13 @@
         <v>13</v>
       </c>
       <c r="E6" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F6:F52)</f>
         <v>Daniel D. Tompkins</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>25000</v>
       </c>
       <c r="H6" s="1">
@@ -1492,13 +1490,13 @@
         <v>13</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F7:F53)</f>
         <v>John C. Calhoun</v>
       </c>
       <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>30000</v>
       </c>
       <c r="H7" s="1">
@@ -1522,13 +1520,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F8:F54)</f>
         <v>John C. Calhoun</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>35000</v>
       </c>
       <c r="H8" s="1">
@@ -1552,13 +1550,13 @@
         <v>26</v>
       </c>
       <c r="E9" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F9:F55)</f>
         <v>Richard Mentor Johnson</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>40000</v>
       </c>
       <c r="H9" s="1">
@@ -1582,13 +1580,13 @@
         <v>33</v>
       </c>
       <c r="E10" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F10:F56)</f>
         <v>John Tyler</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>45000</v>
       </c>
       <c r="H10" s="1">
@@ -1612,13 +1610,13 @@
         <v>37</v>
       </c>
       <c r="E11" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F11:F57)</f>
         <v>Office vacant</v>
       </c>
       <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>50000</v>
       </c>
       <c r="H11" s="1">
@@ -1642,13 +1640,13 @@
         <v>26</v>
       </c>
       <c r="E12" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F12:F58)</f>
         <v>George M. Dallas</v>
       </c>
       <c r="F12" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>55000</v>
       </c>
       <c r="H12" s="1">
@@ -1672,13 +1670,13 @@
         <v>33</v>
       </c>
       <c r="E13" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F13:F59)</f>
         <v>Millard Fillmore</v>
       </c>
       <c r="F13" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>60000</v>
       </c>
       <c r="H13" s="1">
@@ -1702,13 +1700,13 @@
         <v>33</v>
       </c>
       <c r="E14" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F14:F60)</f>
         <v>Office vacant</v>
       </c>
       <c r="F14" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>65000</v>
       </c>
       <c r="H14" s="1">
@@ -1732,13 +1730,13 @@
         <v>26</v>
       </c>
       <c r="E15" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F15:F61)</f>
         <v>William R. King</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>75000</v>
       </c>
       <c r="H15" s="1">
@@ -1762,13 +1760,13 @@
         <v>26</v>
       </c>
       <c r="E16" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F16:F62)</f>
         <v>John C. Breckinridge</v>
       </c>
       <c r="F16" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>85000</v>
       </c>
       <c r="H16" s="1">
@@ -1792,13 +1790,13 @@
         <v>60</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F17:F63)</f>
         <v>Hannibal Hamlin</v>
       </c>
       <c r="F17" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="3">
         <v>95000</v>
       </c>
       <c r="H17" s="1">
@@ -1822,13 +1820,13 @@
         <v>26</v>
       </c>
       <c r="E18" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F18:F64)</f>
         <v>Office vacant</v>
       </c>
       <c r="F18" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>105000</v>
       </c>
       <c r="H18" s="1">
@@ -1852,13 +1850,13 @@
         <v>60</v>
       </c>
       <c r="E19" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F19:F65)</f>
         <v>Schuyler Colfax</v>
       </c>
       <c r="F19" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>115000</v>
       </c>
       <c r="H19" s="1">
@@ -1882,13 +1880,13 @@
         <v>60</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F20:F66)</f>
         <v>William A. Wheeler</v>
       </c>
       <c r="F20" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>125000</v>
       </c>
       <c r="H20" s="1">
@@ -1912,13 +1910,13 @@
         <v>60</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F21:F67)</f>
         <v>Chester A. Arthur</v>
       </c>
       <c r="F21" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>135000</v>
       </c>
       <c r="H21" s="1">
@@ -1942,13 +1940,13 @@
         <v>60</v>
       </c>
       <c r="E22" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F22:F68)</f>
         <v>Office vacant</v>
       </c>
       <c r="F22" t="s">
         <v>38</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="3">
         <v>145000</v>
       </c>
       <c r="H22" s="1">
@@ -1972,13 +1970,13 @@
         <v>26</v>
       </c>
       <c r="E23" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F23:F69)</f>
         <v>Thomas A. Hendricks</v>
       </c>
       <c r="F23" t="s">
         <v>71</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="3">
         <v>155000</v>
       </c>
       <c r="H23" s="1">
@@ -2002,13 +2000,13 @@
         <v>60</v>
       </c>
       <c r="E24" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F24:F70)</f>
         <v>Levi P. Morton</v>
       </c>
       <c r="F24" t="s">
         <v>74</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="3">
         <v>165000</v>
       </c>
       <c r="H24" s="1">
@@ -2032,13 +2030,13 @@
         <v>26</v>
       </c>
       <c r="E25" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F25:F71)</f>
         <v>Adlai Stevenson</v>
       </c>
       <c r="F25" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="3">
         <v>175000</v>
       </c>
       <c r="H25" s="1">
@@ -2062,13 +2060,13 @@
         <v>60</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F26:F72)</f>
         <v>Garret Hobart</v>
       </c>
       <c r="F26" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="3">
         <v>185000</v>
       </c>
       <c r="H26" s="1">
@@ -2092,13 +2090,13 @@
         <v>60</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F27:F73)</f>
         <v>Office vacant</v>
       </c>
       <c r="F27" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="3">
         <v>195000</v>
       </c>
       <c r="H27" s="1">
@@ -2122,13 +2120,13 @@
         <v>60</v>
       </c>
       <c r="E28" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F28:F74)</f>
         <v>James S. Sherman</v>
       </c>
       <c r="F28" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="3">
         <v>205000</v>
       </c>
       <c r="H28" s="1">
@@ -2152,13 +2150,13 @@
         <v>26</v>
       </c>
       <c r="E29" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F29:F75)</f>
         <v>Thomas R. Marshall</v>
       </c>
       <c r="F29" t="s">
         <v>87</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="3">
         <v>225000</v>
       </c>
       <c r="H29" s="1">
@@ -2182,13 +2180,13 @@
         <v>133</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F30:F76)</f>
         <v>Thomas R. Marshall</v>
       </c>
       <c r="F30" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="3">
         <v>225000</v>
       </c>
       <c r="H30" s="1">
@@ -2212,13 +2210,13 @@
         <v>60</v>
       </c>
       <c r="E31" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F31:F77)</f>
         <v>Calvin Coolidge</v>
       </c>
       <c r="F31" t="s">
         <v>90</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="3">
         <v>235000</v>
       </c>
       <c r="H31" s="1">
@@ -2242,13 +2240,13 @@
         <v>60</v>
       </c>
       <c r="E32" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F32:F78)</f>
         <v>Office vacant</v>
       </c>
       <c r="F32" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="3">
         <v>245000</v>
       </c>
       <c r="H32" s="1">
@@ -2272,13 +2270,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F33:F79)</f>
         <v>Charles Curtis</v>
       </c>
       <c r="F33" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="3">
         <v>255000</v>
       </c>
       <c r="H33" s="1">
@@ -2302,13 +2300,13 @@
         <v>26</v>
       </c>
       <c r="E34" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F34:F80)</f>
         <v>John Nance Garner</v>
       </c>
       <c r="F34" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="3">
         <v>265000</v>
       </c>
       <c r="H34" s="1">
@@ -2332,13 +2330,13 @@
         <v>26</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F35:F81)</f>
         <v>Office vacant</v>
       </c>
       <c r="F35" t="s">
         <v>38</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="3">
         <v>275000</v>
       </c>
       <c r="H35" s="1">
@@ -2362,13 +2360,13 @@
         <v>60</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F36:F82)</f>
         <v>Richard Nixon</v>
       </c>
       <c r="F36" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="3">
         <v>285000</v>
       </c>
       <c r="H36" s="1">
@@ -2392,13 +2390,13 @@
         <v>26</v>
       </c>
       <c r="E37" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F37:F83)</f>
         <v>Lyndon B. Johnson</v>
       </c>
       <c r="F37" t="s">
         <v>105</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="3">
         <v>295000</v>
       </c>
       <c r="H37" s="1">
@@ -2422,13 +2420,13 @@
         <v>26</v>
       </c>
       <c r="E38" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F38:F84)</f>
         <v>Office vacant</v>
       </c>
       <c r="F38" t="s">
         <v>38</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="3">
         <v>305000</v>
       </c>
       <c r="H38" s="1">
@@ -2452,13 +2450,13 @@
         <v>60</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F39:F85)</f>
         <v>Spiro Agnew</v>
       </c>
       <c r="F39" t="s">
         <v>108</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="3">
         <v>315000</v>
       </c>
       <c r="H39" s="1">
@@ -2482,13 +2480,13 @@
         <v>60</v>
       </c>
       <c r="E40" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F40:F86)</f>
         <v>Office vacant</v>
       </c>
       <c r="F40" t="s">
         <v>38</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="3">
         <v>325000</v>
       </c>
       <c r="H40" s="1">
@@ -2512,13 +2510,13 @@
         <v>26</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F41:F87)</f>
         <v>Walter Mondale</v>
       </c>
       <c r="F41" t="s">
         <v>113</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="3">
         <v>335000</v>
       </c>
       <c r="H41" s="1">
@@ -2542,13 +2540,13 @@
         <v>60</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F42:F88)</f>
         <v>George H. W. Bush</v>
       </c>
       <c r="F42" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="3">
         <v>345000</v>
       </c>
       <c r="H42" s="1">
@@ -2572,13 +2570,13 @@
         <v>60</v>
       </c>
       <c r="E43" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F43:F89)</f>
         <v>Dan Quayle</v>
       </c>
       <c r="F43" t="s">
         <v>118</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="3">
         <v>355000</v>
       </c>
       <c r="H43" s="1">
@@ -2602,13 +2600,13 @@
         <v>26</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F44:F90)</f>
         <v>Al Gore</v>
       </c>
       <c r="F44" t="s">
         <v>121</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="3">
         <v>365000</v>
       </c>
       <c r="H44" s="1">
@@ -2632,13 +2630,13 @@
         <v>60</v>
       </c>
       <c r="E45" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F45:F91)</f>
         <v>Dick Cheney</v>
       </c>
       <c r="F45" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="3">
         <v>375000</v>
       </c>
       <c r="H45" s="1">
@@ -2662,81 +2660,54 @@
         <v>26</v>
       </c>
       <c r="E46" t="str">
-        <f t="shared" si="0"/>
+        <f>TRIM(F46:F92)</f>
         <v>Joe Biden</v>
       </c>
       <c r="F46" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="3">
         <v>395000</v>
       </c>
-      <c r="H46" s="2">
-        <v>44391</v>
-      </c>
-      <c r="I46" s="2">
+      <c r="H46" s="1">
+        <v>44391</v>
+      </c>
+      <c r="I46" s="1">
         <v>43862</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="E47" t="str">
-        <f t="shared" si="0"/>
-        <v>Joe Biden</v>
+        <f>TRIM(F47:F93)</f>
+        <v>Mike Pence</v>
       </c>
       <c r="F47" t="s">
-        <v>127</v>
-      </c>
-      <c r="G47" s="4">
-        <v>395000</v>
-      </c>
-      <c r="H47" s="2">
-        <v>44391</v>
-      </c>
-      <c r="I47" s="2">
+        <v>130</v>
+      </c>
+      <c r="G47" s="3">
+        <v>405000</v>
+      </c>
+      <c r="H47" s="1">
+        <v>44391</v>
+      </c>
+      <c r="I47" s="1">
         <v>43862</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>45</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>129</v>
-      </c>
-      <c r="D48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E48" t="str">
-        <f t="shared" si="0"/>
-        <v>Mike Pence</v>
-      </c>
-      <c r="F48" t="s">
-        <v>130</v>
-      </c>
-      <c r="G48" s="4">
-        <v>405000</v>
-      </c>
-      <c r="H48" s="2">
-        <v>44391</v>
-      </c>
-      <c r="I48" s="2">
-        <v>43862</v>
-      </c>
+      <c r="G48"/>
     </row>
   </sheetData>
   <dataConsolidate/>
